--- a/data/trans_bre/P6906-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P6906-Edad-trans_bre.xlsx
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-17,89; 17,2</t>
+          <t>-18,51; 16,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-66,24; 10,05</t>
+          <t>-70,45; 9,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-31,22; 34,69</t>
+          <t>-26,93; 36,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,31</t>
+          <t>0,0; 52,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 394,33</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 91,85</t>
+          <t>-100,0; 62,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-15,95; 9,18</t>
+          <t>-15,52; 9,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 22,51</t>
+          <t>-7,28; 22,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 27,34</t>
+          <t>-3,39; 29,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-16,84; 23,53</t>
+          <t>-17,19; 24,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-48,48; 40,97</t>
+          <t>-49,05; 42,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-29,73; 142,73</t>
+          <t>-27,66; 142,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-16,16; 206,93</t>
+          <t>-16,13; 252,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-51,34; 232,92</t>
+          <t>-51,23; 241,94</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,21; 11,33</t>
+          <t>-12,32; 12,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 28,89</t>
+          <t>-1,36; 27,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,13; 18,65</t>
+          <t>-7,98; 18,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 17,95</t>
+          <t>-6,89; 19,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-50,31; 66,25</t>
+          <t>-45,63; 75,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,82; 175,92</t>
+          <t>-8,56; 156,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-33,2; 102,12</t>
+          <t>-28,8; 101,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-23,81; 135,51</t>
+          <t>-26,28; 139,02</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,73; 21,15</t>
+          <t>-11,33; 21,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-26,53; 5,8</t>
+          <t>-25,44; 7,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,35; 25,11</t>
+          <t>-7,65; 25,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,43; 12,82</t>
+          <t>-13,66; 11,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-43,41; 118,14</t>
+          <t>-41,31; 117,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-76,02; 28,71</t>
+          <t>-74,56; 33,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-27,54; 129,1</t>
+          <t>-23,53; 145,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-55,03; 86,34</t>
+          <t>-55,22; 77,24</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-19,61; 26,37</t>
+          <t>-18,38; 26,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-19,38; 30,14</t>
+          <t>-17,81; 30,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,5; 35,35</t>
+          <t>-13,38; 36,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,15; 32,52</t>
+          <t>6,59; 31,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 314,2</t>
+          <t>-100,0; 323,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-58,2; 164,91</t>
+          <t>-59,54; 178,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-29,35; 164,46</t>
+          <t>-35,54; 159,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>23,16; 322,82</t>
+          <t>25,37; 323,55</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,02</t>
+          <t>0,0; 74,74</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 5,66</t>
+          <t>-7,47; 6,84</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 12,51</t>
+          <t>-4,43; 12,31</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,7; 17,14</t>
+          <t>0,83; 16,8</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 12,86</t>
+          <t>-2,77; 12,5</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-29,87; 28,61</t>
+          <t>-29,74; 33,56</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-14,34; 54,22</t>
+          <t>-14,58; 53,88</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,76; 81,76</t>
+          <t>2,24; 80,58</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 82,42</t>
+          <t>-11,65; 80,99</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P6906-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P6906-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17,53</t>
+          <t>17,74</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-18,51; 16,75</t>
+          <t>-19,28; 14,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-70,45; 9,73</t>
+          <t>-72,43; 8,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-26,93; 36,58</t>
+          <t>-28,37; 36,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,52</t>
+          <t>0,0; 56,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 395,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 62,36</t>
+          <t>-100,0; 56,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,03</t>
+          <t>-1,05</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>-3,96%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-15,52; 9,38</t>
+          <t>-15,44; 9,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 22,97</t>
+          <t>-8,2; 22,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 29,55</t>
+          <t>-4,91; 27,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-17,19; 24,26</t>
+          <t>-22,89; 18,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-49,05; 42,53</t>
+          <t>-48,36; 44,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-27,66; 142,24</t>
+          <t>-27,71; 134,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-16,13; 252,23</t>
+          <t>-20,22; 215,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-51,23; 241,94</t>
+          <t>-58,54; 122,05</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,99</t>
+          <t>6,18</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>31,17%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,32; 12,27</t>
+          <t>-13,77; 11,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 27,06</t>
+          <t>0,48; 30,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,98; 18,12</t>
+          <t>-9,83; 16,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 19,31</t>
+          <t>-5,0; 17,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-45,63; 75,2</t>
+          <t>-51,61; 68,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 156,39</t>
+          <t>1,0; 192,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-28,8; 101,48</t>
+          <t>-34,13; 91,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-26,28; 139,02</t>
+          <t>-19,07; 125,18</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,61</t>
+          <t>5,89</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>27,98%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,33; 21,75</t>
+          <t>-10,76; 21,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-25,44; 7,1</t>
+          <t>-26,41; 7,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 25,58</t>
+          <t>-6,58; 26,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,66; 11,48</t>
+          <t>-5,49; 16,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-41,31; 117,46</t>
+          <t>-42,79; 125,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-74,56; 33,68</t>
+          <t>-72,09; 40,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-23,53; 145,75</t>
+          <t>-22,15; 148,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-55,22; 77,24</t>
+          <t>-20,7; 115,47</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20,29</t>
+          <t>20,75</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>126,92%</t>
+          <t>126,65%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-18,38; 26,06</t>
+          <t>-18,89; 24,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-17,81; 30,56</t>
+          <t>-19,44; 32,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,38; 36,28</t>
+          <t>-13,87; 37,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,59; 31,83</t>
+          <t>7,36; 31,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 323,28</t>
+          <t>-100,0; 271,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-59,54; 178,49</t>
+          <t>-60,05; 172,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-35,54; 159,53</t>
+          <t>-34,85; 160,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>25,37; 323,55</t>
+          <t>29,11; 331,16</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19,41</t>
+          <t>18,96</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 74,74</t>
+          <t>0,0; 72,17</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6,2</t>
+          <t>7,7</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>38,3%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 6,84</t>
+          <t>-7,67; 5,98</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 12,31</t>
+          <t>-4,49; 11,06</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,83; 16,8</t>
+          <t>0,82; 16,82</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 12,5</t>
+          <t>1,0; 14,12</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-29,74; 33,56</t>
+          <t>-31,36; 29,97</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-14,58; 53,88</t>
+          <t>-16,32; 45,67</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,24; 80,58</t>
+          <t>2,56; 82,42</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 80,99</t>
+          <t>4,37; 86,71</t>
         </is>
       </c>
     </row>
